--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/nov-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/nov-2025.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2144.22</v>
+        <v>2126.06</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2232.69</v>
+        <v>2213.78</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1671.94</v>
+        <v>1657.78</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5904.74</v>
+        <v>5854.73</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1209.52</v>
+        <v>1199.28</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3699.8</v>
+        <v>3668.47</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3059.71</v>
+        <v>3033.79</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6483.53</v>
+        <v>6428.62</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2328.07</v>
+        <v>2308.35</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2229.27</v>
+        <v>2210.39</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3366.54</v>
+        <v>3338.03</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4761.26</v>
+        <v>4720.94</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2277.29</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>5585.04</v>
+        <v>5537.74</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>11927.11</v>
+        <v>11826.09</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2355.62</v>
+        <v>2335.67</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1831.73</v>
+        <v>1816.22</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2269.36</v>
+        <v>2250.14</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5673.79</v>
+        <v>5644.63</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1649.97</v>
+        <v>1641.5</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7476.11</v>
+        <v>7437.7</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3044.64</v>
+        <v>3028.99</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>5733.92</v>
+        <v>5704.45</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>4433.19</v>
+        <v>4410.41</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2849.78</v>
+        <v>2835.13</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2234.52</v>
+        <v>2223.04</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>32057.9</v>
+        <v>31893.18</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1982.45</v>
+        <v>1972.26</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2270.43</v>
+        <v>2258.76</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>765.25</v>
+        <v>761.3200000000001</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>4244.47</v>
+        <v>4222.66</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>27310.84</v>
+        <v>27170.52</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>851.8099999999999</v>
+        <v>847.4299999999999</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>4251.63</v>
+        <v>4229.79</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3171.82</v>
+        <v>3155.52</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>6759.21</v>
+        <v>6724.48</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>24528.16</v>
+        <v>24402.13</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2420.16</v>
+        <v>2407.73</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>4152.38</v>
+        <v>4131.05</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2868.55</v>
+        <v>2853.81</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2857.69</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2244.7</v>
+        <v>2233.17</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3262.66</v>
+        <v>3245.9</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>20464.79</v>
+        <v>20359.64</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>23619.75</v>
+        <v>23498.39</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>7431.92</v>
+        <v>7393.73</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3472.94</v>
+        <v>3455.1</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1385.81</v>
+        <v>1378.69</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2830.2</v>
+        <v>2815.66</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>9206.02</v>
+        <v>9114.15</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>11338.16</v>
+        <v>11225</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>775</v>
+        <v>767.27</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2412.44</v>
+        <v>2388.36</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2137.92</v>
+        <v>2116.59</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>22845.43</v>
+        <v>22617.43</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2248.81</v>
+        <v>2226.37</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1682.32</v>
+        <v>1665.53</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>7344.52</v>
+        <v>7271.22</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>4454.51</v>
+        <v>4410.06</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>4273.18</v>
+        <v>4230.53</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3954.12</v>
+        <v>3914.66</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>41391.3</v>
+        <v>40978.21</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3596.78</v>
+        <v>3560.88</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>3155.79</v>
+        <v>3124.3</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>31730.87</v>
+        <v>31414.2</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2860.3</v>
+        <v>2831.75</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>744.21</v>
+        <v>736.78</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>5559.66</v>
+        <v>5504.18</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2711.33</v>
+        <v>2684.27</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>7423.1</v>
+        <v>7349.01</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2268.67</v>
+        <v>2246.03</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>4919.24</v>
+        <v>4870.14</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>875.46</v>
+        <v>866.72</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>7552.62</v>
+        <v>7477.24</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>3217.6</v>
+        <v>3185.49</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2698.14</v>
+        <v>2671.21</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>5711.3</v>
+        <v>5654.3</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>744.92</v>
+        <v>737.49</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>8995.540000000001</v>
+        <v>8905.77</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>24883.62</v>
+        <v>24623.03</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2652.88</v>
+        <v>2625.1</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2388.91</v>
+        <v>2363.89</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2876.62</v>
+        <v>2846.49</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>11783.66</v>
+        <v>11660.26</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1693.31</v>
+        <v>1675.58</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>4868.67</v>
+        <v>4817.69</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1352</v>
+        <v>1337.84</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>18759.47</v>
+        <v>18563.02</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>10515.06</v>
+        <v>10404.95</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>3220.82</v>
+        <v>3187.09</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>4385.43</v>
+        <v>4339.5</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>4254.57</v>
+        <v>4210.02</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2953.07</v>
+        <v>2922.14</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>21697.32</v>
+        <v>21470.1</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2656.81</v>
+        <v>2628.99</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3827.4</v>
+        <v>3787.32</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>2095.71</v>
+        <v>2073.77</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1384.55</v>
+        <v>1370.05</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2259.02</v>
+        <v>2235.37</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1404.28</v>
+        <v>1389.57</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>23353.14</v>
+        <v>23108.58</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2128.36</v>
+        <v>2106.07</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1712.02</v>
+        <v>1694.1</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>31453.63</v>
+        <v>31124.24</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>10717.74</v>
+        <v>10605.5</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>18748.56</v>
+        <v>18552.22</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2192.55</v>
+        <v>2169.59</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>4105.85</v>
+        <v>4062.85</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>25793.53</v>
+        <v>25523.41</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>2371.34</v>
+        <v>2346.51</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>883.9400000000001</v>
+        <v>874.6799999999999</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>3814.19</v>
+        <v>3774.25</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>6240.21</v>
+        <v>6206.1</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>4184.33</v>
+        <v>4161.46</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>768.8099999999999</v>
+        <v>764.61</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>3220.11</v>
+        <v>3202.51</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>3303.38</v>
+        <v>3285.33</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>3205.48</v>
+        <v>3187.96</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>3449.32</v>
+        <v>3430.46</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>10678.11</v>
+        <v>10619.74</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>3274.77</v>
+        <v>3256.87</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2638.2</v>
+        <v>2623.78</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1750.48</v>
+        <v>1740.91</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2244.66</v>
+        <v>2232.39</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>10274.06</v>
+        <v>10217.91</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2264.49</v>
+        <v>2252.11</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>3152.54</v>
+        <v>3135.31</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>9312.219999999999</v>
+        <v>9261.32</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2383.28</v>
+        <v>2370.25</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1446.97</v>
+        <v>1439.07</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>3423.63</v>
+        <v>3404.91</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>4065.09</v>
+        <v>4042.87</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2171.77</v>
+        <v>2159.9</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>25184.65</v>
+        <v>25047</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>3676.16</v>
+        <v>3656.07</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>8714.23</v>
+        <v>8666.6</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2226.99</v>
+        <v>2214.81</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>8503.01</v>
+        <v>8456.530000000001</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>5041.3</v>
+        <v>5013.74</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1576.94</v>
+        <v>1568.32</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>22243.41</v>
+        <v>22121.83</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>10678.33</v>
+        <v>10619.97</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1206.64</v>
+        <v>1200.04</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2649.37</v>
+        <v>2619.85</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2173.09</v>
+        <v>2148.88</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>5399.97</v>
+        <v>5339.81</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>8432.4</v>
+        <v>8338.450000000001</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>2244.04</v>
+        <v>2219.03</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2953.07</v>
+        <v>2920.17</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>2459.99</v>
+        <v>2432.58</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>745.45</v>
+        <v>737.15</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2171.12</v>
+        <v>2146.93</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>2596.4</v>
+        <v>2567.48</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>7628.16</v>
+        <v>7543.17</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1724.54</v>
+        <v>1705.33</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>5140.3</v>
+        <v>5083.03</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>11010.83</v>
+        <v>10888.15</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>1837.08</v>
+        <v>1816.62</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1306.91</v>
+        <v>1292.35</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>5951.82</v>
+        <v>5885.5</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>3137.73</v>
+        <v>3102.77</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>3164.6</v>
+        <v>3129.35</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>9243.32</v>
+        <v>9140.33</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>2811.8</v>
+        <v>2780.47</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>9343.030000000001</v>
+        <v>9238.93</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1111.47</v>
+        <v>1099.09</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>9113.059999999999</v>
+        <v>9011.52</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>4278.9</v>
+        <v>4231.23</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>11878</v>
+        <v>11745.66</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>3077.86</v>
+        <v>3043.56</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1092.02</v>
+        <v>1079.86</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>2520.95</v>
+        <v>2492.87</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>52897.02</v>
+        <v>52307.67</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>2661.7</v>
+        <v>2632.04</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>6800.96</v>
+        <v>6725.19</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>10353.3</v>
+        <v>10296.6</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>2411.9</v>
+        <v>2398.69</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>1611.09</v>
+        <v>1602.27</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>3032.85</v>
+        <v>3016.24</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>3894.19</v>
+        <v>3872.86</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>2010.22</v>
+        <v>1999.21</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2719.57</v>
+        <v>2704.68</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1916.39</v>
+        <v>1905.89</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>20402.36</v>
+        <v>20290.63</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>1281.99</v>
+        <v>1274.97</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>2261.16</v>
+        <v>2248.78</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>3077.69</v>
+        <v>3060.83</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>2202.21</v>
+        <v>2190.15</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>2230.33</v>
+        <v>2218.12</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1712.03</v>
+        <v>1702.66</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>2140.11</v>
+        <v>2128.39</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>2871.85</v>
+        <v>2856.13</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>6080.46</v>
+        <v>6047.16</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1863.39</v>
+        <v>1853.18</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>4555.05</v>
+        <v>4530.1</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>2312.28</v>
+        <v>2299.61</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>2659.89</v>
+        <v>2645.32</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>10658.18</v>
+        <v>10599.81</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>2359.09</v>
+        <v>2346.17</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>9893.42</v>
+        <v>9839.24</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>3201.61</v>
+        <v>3184.07</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>4504</v>
+        <v>4479.34</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>2732.52</v>
+        <v>2717.55</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>3419.7</v>
+        <v>3400.98</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>3531.09</v>
+        <v>3511.76</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1081.65</v>
+        <v>1075.72</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>9801.01</v>
+        <v>9747.34</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>2281.88</v>
+        <v>2269.38</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>2236.47</v>
+        <v>2224.23</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>14066.66</v>
+        <v>13989.62</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>3475.64</v>
+        <v>3471.22</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>7428.46</v>
+        <v>7419</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>2169.71</v>
+        <v>2166.94</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>9214.040000000001</v>
+        <v>9202.309999999999</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>4931.64</v>
+        <v>4925.36</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>12595.69</v>
+        <v>12579.66</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>969.73</v>
+        <v>968.5</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>2033.23</v>
+        <v>2030.64</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>4194.6</v>
+        <v>4189.26</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>6394.9</v>
+        <v>6386.76</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>3515.45</v>
+        <v>3510.98</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>1087.26</v>
+        <v>1085.87</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>2782.08</v>
+        <v>2778.54</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>5946.96</v>
+        <v>5939.39</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>14599.12</v>
+        <v>14580.54</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>2403.66</v>
+        <v>2400.6</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>2299.38</v>
+        <v>2296.45</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>7893.49</v>
+        <v>7883.44</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>746.8</v>
+        <v>745.85</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>4204.7</v>
+        <v>4199.35</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>3655.85</v>
+        <v>3651.2</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>2781.63</v>
+        <v>2778.09</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>3004.89</v>
+        <v>3001.07</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>1163.56</v>
+        <v>1162.08</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>2254.42</v>
+        <v>2251.55</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>7198.12</v>
+        <v>7188.96</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>15323.4</v>
+        <v>15303.89</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>3499.43</v>
+        <v>3494.97</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>7749.43</v>
+        <v>7739.57</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>3126.56</v>
+        <v>3122.58</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>35906.63</v>
+        <v>35860.93</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>2900.17</v>
+        <v>2896.48</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>7480.26</v>
+        <v>7470.73</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>2776.87</v>
+        <v>2773.34</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>5165.85</v>
+        <v>5159.27</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>1083.94</v>
+        <v>1082.56</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>9339.940000000001</v>
+        <v>9328.049999999999</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>2804.27</v>
+        <v>2800.7</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>2546.84</v>
+        <v>2543.6</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>1260.67</v>
+        <v>1259.06</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>2184.13</v>
+        <v>2181.35</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>2726</v>
+        <v>2722.53</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>2847.9</v>
+        <v>2844.28</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>2863.5</v>
+        <v>2859.85</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>2131.45</v>
+        <v>2128.74</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>5203.55</v>
+        <v>5196.92</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>749.9400000000001</v>
+        <v>748.99</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>1414.73</v>
+        <v>1412.93</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1190.43</v>
+        <v>1188.91</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>2547.16</v>
+        <v>2543.92</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>4633.09</v>
+        <v>4627.19</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>2523.05</v>
+        <v>2519.84</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>13284.87</v>
+        <v>13267.96</v>
       </c>
     </row>
     <row r="265">
@@ -16616,7 +16616,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>937.9400000000001</v>
+        <v>936.74</v>
       </c>
     </row>
     <row r="266">
@@ -16677,7 +16677,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>1068.98</v>
+        <v>1067.62</v>
       </c>
     </row>
     <row r="267">
@@ -16738,7 +16738,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>2481.84</v>
+        <v>2478.68</v>
       </c>
     </row>
     <row r="268">
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>3942.23</v>
+        <v>3937.22</v>
       </c>
     </row>
     <row r="269">
@@ -16860,7 +16860,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>2709.02</v>
+        <v>2705.58</v>
       </c>
     </row>
     <row r="270">
@@ -16921,7 +16921,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>2906.7</v>
+        <v>2903</v>
       </c>
     </row>
     <row r="271">
@@ -16982,7 +16982,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>1783.29</v>
+        <v>1781.02</v>
       </c>
     </row>
     <row r="272">
@@ -17043,7 +17043,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>6565.79</v>
+        <v>6589.22</v>
       </c>
     </row>
     <row r="273">
@@ -17104,7 +17104,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>8883.370000000001</v>
+        <v>8915.08</v>
       </c>
     </row>
     <row r="274">
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>2246.9</v>
+        <v>2254.91</v>
       </c>
     </row>
     <row r="275">
@@ -17226,7 +17226,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>943.02</v>
+        <v>946.39</v>
       </c>
     </row>
     <row r="276">
@@ -17287,7 +17287,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>1864.68</v>
+        <v>1871.34</v>
       </c>
     </row>
     <row r="277">
@@ -17348,7 +17348,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2204.24</v>
+        <v>2212.11</v>
       </c>
     </row>
     <row r="278">
@@ -17409,7 +17409,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>7313.33</v>
+        <v>7339.43</v>
       </c>
     </row>
     <row r="279">
@@ -17470,7 +17470,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>6512.32</v>
+        <v>6535.56</v>
       </c>
     </row>
     <row r="280">
@@ -17531,7 +17531,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>7497.13</v>
+        <v>7523.89</v>
       </c>
     </row>
     <row r="281">
@@ -17592,7 +17592,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>10206.88</v>
+        <v>10243.3</v>
       </c>
     </row>
     <row r="282">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>2229.8</v>
+        <v>2237.75</v>
       </c>
     </row>
     <row r="283">
@@ -17714,7 +17714,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>1396.62</v>
+        <v>1401.6</v>
       </c>
     </row>
     <row r="284">
@@ -17775,7 +17775,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>36914.38</v>
+        <v>37046.13</v>
       </c>
     </row>
     <row r="285">
@@ -17836,7 +17836,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>7890.88</v>
+        <v>7919.04</v>
       </c>
     </row>
     <row r="286">
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>1052.85</v>
+        <v>1056.61</v>
       </c>
     </row>
     <row r="287">
@@ -17958,7 +17958,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>13301.27</v>
+        <v>13348.75</v>
       </c>
     </row>
     <row r="288">
@@ -18019,7 +18019,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>4221.99</v>
+        <v>4237.05</v>
       </c>
     </row>
     <row r="289">
@@ -18080,7 +18080,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>17754.66</v>
+        <v>17818.03</v>
       </c>
     </row>
     <row r="290">
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>8577.02</v>
+        <v>8607.629999999999</v>
       </c>
     </row>
     <row r="291">
@@ -18202,7 +18202,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>945.83</v>
+        <v>949.21</v>
       </c>
     </row>
     <row r="292">
@@ -18263,7 +18263,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>1627.28</v>
+        <v>1633.09</v>
       </c>
     </row>
     <row r="293">
@@ -18324,7 +18324,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>14635.63</v>
+        <v>14687.86</v>
       </c>
     </row>
     <row r="294">
@@ -18385,7 +18385,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>10130.01</v>
+        <v>10166.16</v>
       </c>
     </row>
     <row r="295">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>1241.76</v>
+        <v>1246.2</v>
       </c>
     </row>
     <row r="296">
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>6147.36</v>
+        <v>6169.3</v>
       </c>
     </row>
     <row r="297">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>2247.42</v>
+        <v>2255.44</v>
       </c>
     </row>
     <row r="298">
@@ -18629,7 +18629,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>4422.81</v>
+        <v>4438.59</v>
       </c>
     </row>
     <row r="299">
@@ -18690,7 +18690,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>1212.26</v>
+        <v>1216.59</v>
       </c>
     </row>
     <row r="300">
@@ -18751,7 +18751,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>2515.96</v>
+        <v>2524.94</v>
       </c>
     </row>
     <row r="301">
@@ -18812,7 +18812,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>826.0599999999999</v>
+        <v>829.01</v>
       </c>
     </row>
     <row r="302">
@@ -18873,7 +18873,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>20807.1</v>
+        <v>20881.35</v>
       </c>
     </row>
     <row r="303">
@@ -18934,7 +18934,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>750.3</v>
+        <v>752.98</v>
       </c>
     </row>
     <row r="304">
@@ -18995,7 +18995,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>10605.96</v>
+        <v>10643.81</v>
       </c>
     </row>
     <row r="305">
@@ -19056,7 +19056,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>6634.07</v>
+        <v>6657.74</v>
       </c>
     </row>
     <row r="306">
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>2263.36</v>
+        <v>2271.44</v>
       </c>
     </row>
     <row r="307">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>2287.62</v>
+        <v>2312.51</v>
       </c>
     </row>
     <row r="308">
@@ -19239,7 +19239,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>2217.15</v>
+        <v>2241.27</v>
       </c>
     </row>
     <row r="309">
@@ -19300,7 +19300,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>2219.88</v>
+        <v>2244.02</v>
       </c>
     </row>
     <row r="310">
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>5134.1</v>
+        <v>5189.94</v>
       </c>
     </row>
     <row r="311">
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>2413.28</v>
+        <v>2439.52</v>
       </c>
     </row>
     <row r="312">
@@ -19483,7 +19483,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>4655.98</v>
+        <v>4706.62</v>
       </c>
     </row>
     <row r="313">
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>2187.46</v>
+        <v>2211.25</v>
       </c>
     </row>
     <row r="314">
@@ -19605,7 +19605,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>4026.98</v>
+        <v>4070.78</v>
       </c>
     </row>
     <row r="315">
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>11250.41</v>
+        <v>11372.77</v>
       </c>
     </row>
     <row r="316">
@@ -19727,7 +19727,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>2277.18</v>
+        <v>2301.95</v>
       </c>
     </row>
     <row r="317">
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>981.4</v>
+        <v>992.0700000000001</v>
       </c>
     </row>
     <row r="318">
@@ -19849,7 +19849,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>3548.52</v>
+        <v>3587.11</v>
       </c>
     </row>
     <row r="319">
@@ -19910,7 +19910,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>1229.74</v>
+        <v>1243.12</v>
       </c>
     </row>
     <row r="320">
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>1018.31</v>
+        <v>1029.39</v>
       </c>
     </row>
     <row r="321">
@@ -20032,7 +20032,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>4975.66</v>
+        <v>5029.77</v>
       </c>
     </row>
     <row r="322">
@@ -20093,7 +20093,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>1142.12</v>
+        <v>1154.54</v>
       </c>
     </row>
     <row r="323">
@@ -20154,7 +20154,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>3021.78</v>
+        <v>3054.64</v>
       </c>
     </row>
     <row r="324">
@@ -20215,7 +20215,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>2227.91</v>
+        <v>2252.14</v>
       </c>
     </row>
     <row r="325">
@@ -20276,7 +20276,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>5990.08</v>
+        <v>6055.23</v>
       </c>
     </row>
     <row r="326">
@@ -20337,7 +20337,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>8545.969999999999</v>
+        <v>8638.92</v>
       </c>
     </row>
     <row r="327">
@@ -20398,7 +20398,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>2712.74</v>
+        <v>2742.25</v>
       </c>
     </row>
     <row r="328">
@@ -20459,7 +20459,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>7980</v>
+        <v>8066.79</v>
       </c>
     </row>
     <row r="329">
@@ -20520,7 +20520,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>4566.19</v>
+        <v>4615.86</v>
       </c>
     </row>
     <row r="330">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>8311.709999999999</v>
+        <v>8402.110000000001</v>
       </c>
     </row>
     <row r="331">
@@ -20642,7 +20642,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>748.85</v>
+        <v>756.99</v>
       </c>
     </row>
     <row r="332">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>2400.13</v>
+        <v>2426.23</v>
       </c>
     </row>
     <row r="333">
@@ -20764,7 +20764,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>6202.49</v>
+        <v>6269.95</v>
       </c>
     </row>
     <row r="334">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>1169.78</v>
+        <v>1182.5</v>
       </c>
     </row>
     <row r="335">
@@ -20886,7 +20886,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>3981.18</v>
+        <v>4024.48</v>
       </c>
     </row>
     <row r="336">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>2243.01</v>
+        <v>2267.41</v>
       </c>
     </row>
     <row r="337">
@@ -21008,7 +21008,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>2352.83</v>
+        <v>2378.42</v>
       </c>
     </row>
     <row r="338">
@@ -21069,7 +21069,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>2902.73</v>
+        <v>2934.3</v>
       </c>
     </row>
     <row r="339">
@@ -21130,7 +21130,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>3371.89</v>
+        <v>3408.57</v>
       </c>
     </row>
     <row r="340">
@@ -21191,7 +21191,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>917.72</v>
+        <v>927.7</v>
       </c>
     </row>
     <row r="341">
@@ -21252,7 +21252,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>1516.31</v>
+        <v>1532.81</v>
       </c>
     </row>
     <row r="342">
@@ -21313,7 +21313,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>2676.15</v>
+        <v>2705.26</v>
       </c>
     </row>
     <row r="343">
@@ -21374,7 +21374,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>6741.06</v>
+        <v>6814.38</v>
       </c>
     </row>
     <row r="344">
@@ -21435,7 +21435,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>999.41</v>
+        <v>1010.28</v>
       </c>
     </row>
     <row r="345">
@@ -21496,7 +21496,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>3094.44</v>
+        <v>3128.1</v>
       </c>
     </row>
     <row r="346">
@@ -21557,7 +21557,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>2587.51</v>
+        <v>2615.65</v>
       </c>
     </row>
     <row r="347">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>3920.23</v>
+        <v>3962.87</v>
       </c>
     </row>
     <row r="348">
@@ -21679,7 +21679,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>2676.54</v>
+        <v>2705.65</v>
       </c>
     </row>
     <row r="349">
@@ -21740,7 +21740,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>3842.17</v>
+        <v>3883.96</v>
       </c>
     </row>
     <row r="350">
@@ -21801,7 +21801,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>4060.57</v>
+        <v>4104.73</v>
       </c>
     </row>
     <row r="351">
@@ -21862,7 +21862,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>1717.51</v>
+        <v>1736.19</v>
       </c>
     </row>
     <row r="352">
@@ -21923,7 +21923,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>2195.67</v>
+        <v>2219.55</v>
       </c>
     </row>
     <row r="353">
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>13715.18</v>
+        <v>13760.29</v>
       </c>
     </row>
     <row r="354">
@@ -22045,7 +22045,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>6875.23</v>
+        <v>6897.85</v>
       </c>
     </row>
     <row r="355">
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>2320.87</v>
+        <v>2328.5</v>
       </c>
     </row>
     <row r="356">
@@ -22167,7 +22167,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>3692</v>
+        <v>3704.14</v>
       </c>
     </row>
     <row r="357">
@@ -22228,7 +22228,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>3404.99</v>
+        <v>3416.19</v>
       </c>
     </row>
     <row r="358">
@@ -22289,7 +22289,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>2334.55</v>
+        <v>2342.23</v>
       </c>
     </row>
     <row r="359">
@@ -22350,7 +22350,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>2701.8</v>
+        <v>2710.69</v>
       </c>
     </row>
     <row r="360">
@@ -22411,7 +22411,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>5925.6</v>
+        <v>5945.09</v>
       </c>
     </row>
     <row r="361">
@@ -22472,7 +22472,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>8940.690000000001</v>
+        <v>8970.09</v>
       </c>
     </row>
     <row r="362">
@@ -22533,7 +22533,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>6230.51</v>
+        <v>6251</v>
       </c>
     </row>
     <row r="363">
@@ -22594,7 +22594,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>1960.5</v>
+        <v>1966.95</v>
       </c>
     </row>
     <row r="364">
@@ -22655,7 +22655,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>1776.27</v>
+        <v>1782.11</v>
       </c>
     </row>
     <row r="365">
@@ -22716,7 +22716,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>5374.54</v>
+        <v>5392.21</v>
       </c>
     </row>
     <row r="366">
@@ -22777,7 +22777,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>2671.53</v>
+        <v>2680.31</v>
       </c>
     </row>
     <row r="367">
@@ -22838,7 +22838,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>5012.65</v>
+        <v>5029.14</v>
       </c>
     </row>
     <row r="368">
@@ -22899,7 +22899,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>9308.4</v>
+        <v>9339.01</v>
       </c>
     </row>
     <row r="369">
@@ -22960,7 +22960,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>2574.59</v>
+        <v>2583.06</v>
       </c>
     </row>
     <row r="370">
@@ -23021,7 +23021,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>2585.59</v>
+        <v>2594.09</v>
       </c>
     </row>
     <row r="371">
@@ -23082,7 +23082,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>2508.44</v>
+        <v>2516.69</v>
       </c>
     </row>
     <row r="372">
@@ -23143,7 +23143,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>20916.99</v>
+        <v>20985.79</v>
       </c>
     </row>
     <row r="373">
@@ -23204,7 +23204,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>2342.15</v>
+        <v>2349.85</v>
       </c>
     </row>
     <row r="374">
@@ -23265,7 +23265,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>2538.47</v>
+        <v>2546.82</v>
       </c>
     </row>
     <row r="375">
@@ -23326,7 +23326,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>6003.28</v>
+        <v>6023.02</v>
       </c>
     </row>
     <row r="376">
@@ -23387,7 +23387,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>6714.99</v>
+        <v>6737.08</v>
       </c>
     </row>
     <row r="377">
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>2611.94</v>
+        <v>2620.53</v>
       </c>
     </row>
     <row r="378">
@@ -23509,7 +23509,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>6809.16</v>
+        <v>6831.56</v>
       </c>
     </row>
     <row r="379">
@@ -23570,7 +23570,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>6409.76</v>
+        <v>6430.85</v>
       </c>
     </row>
     <row r="380">
@@ -23631,7 +23631,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>773.17</v>
+        <v>775.71</v>
       </c>
     </row>
     <row r="381">
@@ -23692,7 +23692,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>3658.9</v>
+        <v>3670.93</v>
       </c>
     </row>
     <row r="382">
@@ -23753,7 +23753,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>2002.29</v>
+        <v>2008.87</v>
       </c>
     </row>
     <row r="383">
@@ -23814,7 +23814,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>775.71</v>
+        <v>778.26</v>
       </c>
     </row>
     <row r="384">
@@ -23875,7 +23875,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>872.1900000000001</v>
+        <v>875.05</v>
       </c>
     </row>
     <row r="385">
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>2242.08</v>
+        <v>2249.46</v>
       </c>
     </row>
     <row r="386">
@@ -23997,7 +23997,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>3603.78</v>
+        <v>3615.63</v>
       </c>
     </row>
     <row r="387">
@@ -24058,7 +24058,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>1846.88</v>
+        <v>1852.95</v>
       </c>
     </row>
     <row r="388">
@@ -24119,7 +24119,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>1239.35</v>
+        <v>1243.42</v>
       </c>
     </row>
     <row r="389">
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>4150.78</v>
+        <v>4222.43</v>
       </c>
     </row>
     <row r="390">
@@ -24241,7 +24241,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>4772.37</v>
+        <v>4854.75</v>
       </c>
     </row>
     <row r="391">
@@ -24302,7 +24302,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>2082.92</v>
+        <v>2118.87</v>
       </c>
     </row>
     <row r="392">
@@ -24363,7 +24363,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>4391.2</v>
+        <v>4467</v>
       </c>
     </row>
     <row r="393">
@@ -24424,7 +24424,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>21919.59</v>
+        <v>22297.96</v>
       </c>
     </row>
     <row r="394">
@@ -24485,7 +24485,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>7680.98</v>
+        <v>7813.56</v>
       </c>
     </row>
     <row r="395">
@@ -24546,7 +24546,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>1245.94</v>
+        <v>1267.44</v>
       </c>
     </row>
     <row r="396">
@@ -24607,7 +24607,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>6408.14</v>
+        <v>6518.75</v>
       </c>
     </row>
     <row r="397">
@@ -24668,7 +24668,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>977.73</v>
+        <v>994.61</v>
       </c>
     </row>
     <row r="398">
@@ -24729,7 +24729,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>21125.63</v>
+        <v>21490.29</v>
       </c>
     </row>
     <row r="399">
@@ -24790,7 +24790,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>2752.44</v>
+        <v>2799.95</v>
       </c>
     </row>
     <row r="400">
@@ -24851,7 +24851,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>2316.11</v>
+        <v>2356.09</v>
       </c>
     </row>
     <row r="401">
@@ -24912,7 +24912,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>8743.870000000001</v>
+        <v>8894.799999999999</v>
       </c>
     </row>
     <row r="402">
@@ -24973,7 +24973,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>1977.78</v>
+        <v>2011.92</v>
       </c>
     </row>
     <row r="403">
@@ -25034,7 +25034,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>6473.35</v>
+        <v>6585.09</v>
       </c>
     </row>
     <row r="404">
@@ -25095,7 +25095,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>11315.24</v>
+        <v>11510.56</v>
       </c>
     </row>
     <row r="405">
@@ -25156,7 +25156,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>969.53</v>
+        <v>986.26</v>
       </c>
     </row>
     <row r="406">
@@ -25217,7 +25217,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>6955.67</v>
+        <v>7075.74</v>
       </c>
     </row>
     <row r="407">
@@ -25278,7 +25278,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>2261.73</v>
+        <v>2300.77</v>
       </c>
     </row>
     <row r="408">
@@ -25339,7 +25339,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>3497.01</v>
+        <v>3557.37</v>
       </c>
     </row>
     <row r="409">
@@ -25400,7 +25400,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>4427.44</v>
+        <v>4503.87</v>
       </c>
     </row>
     <row r="410">
@@ -25461,7 +25461,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>1317.05</v>
+        <v>1339.79</v>
       </c>
     </row>
     <row r="411">
@@ -25522,7 +25522,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>10682.94</v>
+        <v>10867.34</v>
       </c>
     </row>
     <row r="412">
@@ -25583,7 +25583,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>1525.98</v>
+        <v>1552.32</v>
       </c>
     </row>
     <row r="413">
@@ -25644,7 +25644,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>4034.01</v>
+        <v>4103.64</v>
       </c>
     </row>
     <row r="414">
@@ -25705,7 +25705,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>2544.13</v>
+        <v>2588.04</v>
       </c>
     </row>
     <row r="415">
@@ -25766,7 +25766,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>745.05</v>
+        <v>757.91</v>
       </c>
     </row>
     <row r="416">
@@ -25827,7 +25827,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>6355.71</v>
+        <v>6465.42</v>
       </c>
     </row>
     <row r="417">
@@ -25888,7 +25888,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>8909.33</v>
+        <v>9063.120000000001</v>
       </c>
     </row>
     <row r="418">
@@ -25949,7 +25949,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>2232.62</v>
+        <v>2271.16</v>
       </c>
     </row>
     <row r="419">
@@ -26010,7 +26010,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>3766.07</v>
+        <v>3831.08</v>
       </c>
     </row>
     <row r="420">
@@ -26071,7 +26071,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>3439.23</v>
+        <v>3498.6</v>
       </c>
     </row>
     <row r="421">
@@ -26132,7 +26132,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>7353.04</v>
+        <v>7479.97</v>
       </c>
     </row>
     <row r="422">
@@ -26193,7 +26193,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>1217.09</v>
+        <v>1225.52</v>
       </c>
     </row>
     <row r="423">
@@ -26254,7 +26254,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>2162.02</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="424">
@@ -26315,7 +26315,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>1177.98</v>
+        <v>1186.15</v>
       </c>
     </row>
     <row r="425">
@@ -26376,7 +26376,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>2382.68</v>
+        <v>2399.19</v>
       </c>
     </row>
     <row r="426">
@@ -26437,7 +26437,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>4423.96</v>
+        <v>4454.61</v>
       </c>
     </row>
     <row r="427">
@@ -26498,7 +26498,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>5600.3</v>
+        <v>5639.1</v>
       </c>
     </row>
     <row r="428">
@@ -26559,7 +26559,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>4164</v>
+        <v>4192.85</v>
       </c>
     </row>
     <row r="429">
@@ -26620,7 +26620,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>845.1</v>
+        <v>850.95</v>
       </c>
     </row>
     <row r="430">
@@ -26681,7 +26681,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>4347.48</v>
+        <v>4377.6</v>
       </c>
     </row>
     <row r="431">
@@ -26742,7 +26742,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>1175.64</v>
+        <v>1183.79</v>
       </c>
     </row>
     <row r="432">
@@ -26803,7 +26803,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>8234.77</v>
+        <v>8291.809999999999</v>
       </c>
     </row>
     <row r="433">
@@ -26864,7 +26864,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>8110.99</v>
+        <v>8167.18</v>
       </c>
     </row>
     <row r="434">
@@ -26925,7 +26925,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>5385.78</v>
+        <v>5423.09</v>
       </c>
     </row>
     <row r="435">
@@ -26986,7 +26986,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>1690.8</v>
+        <v>1702.52</v>
       </c>
     </row>
     <row r="436">
@@ -27047,7 +27047,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>6903.41</v>
+        <v>6951.23</v>
       </c>
     </row>
     <row r="437">
@@ -27108,7 +27108,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>1408.77</v>
+        <v>1418.53</v>
       </c>
     </row>
     <row r="438">
@@ -27169,7 +27169,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>3803.53</v>
+        <v>3829.88</v>
       </c>
     </row>
     <row r="439">
@@ -27230,7 +27230,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>5546.33</v>
+        <v>5584.75</v>
       </c>
     </row>
     <row r="440">
@@ -27291,7 +27291,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>14736.73</v>
+        <v>14838.82</v>
       </c>
     </row>
     <row r="441">
@@ -27352,7 +27352,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>2186.57</v>
+        <v>2201.72</v>
       </c>
     </row>
     <row r="442">
@@ -27413,7 +27413,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>2808.31</v>
+        <v>2827.77</v>
       </c>
     </row>
     <row r="443">
@@ -27474,7 +27474,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>2632.71</v>
+        <v>2644.97</v>
       </c>
     </row>
     <row r="444">
@@ -27535,7 +27535,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>4155.1</v>
+        <v>4174.45</v>
       </c>
     </row>
     <row r="445">
@@ -27596,7 +27596,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>2231.97</v>
+        <v>2242.36</v>
       </c>
     </row>
     <row r="446">
@@ -27657,7 +27657,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>1490.27</v>
+        <v>1497.21</v>
       </c>
     </row>
     <row r="447">
@@ -27718,7 +27718,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>3331.25</v>
+        <v>3346.76</v>
       </c>
     </row>
     <row r="448">
@@ -27779,7 +27779,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>9788.82</v>
+        <v>9834.4</v>
       </c>
     </row>
     <row r="449">
@@ -27840,7 +27840,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>5307.45</v>
+        <v>5332.17</v>
       </c>
     </row>
     <row r="450">
@@ -27901,7 +27901,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>2726.4</v>
+        <v>2739.1</v>
       </c>
     </row>
     <row r="451">
@@ -27962,7 +27962,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>2260.46</v>
+        <v>2270.99</v>
       </c>
     </row>
     <row r="452">
@@ -28023,7 +28023,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>6462.38</v>
+        <v>6492.47</v>
       </c>
     </row>
     <row r="453">
@@ -28084,7 +28084,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>809.23</v>
+        <v>813</v>
       </c>
     </row>
     <row r="454">
@@ -28145,7 +28145,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>2567.01</v>
+        <v>2578.96</v>
       </c>
     </row>
     <row r="455">
@@ -28206,7 +28206,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>4816.48</v>
+        <v>4838.91</v>
       </c>
     </row>
     <row r="456">
@@ -28267,7 +28267,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>5230.06</v>
+        <v>5254.42</v>
       </c>
     </row>
     <row r="457">
@@ -28328,7 +28328,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>2783.71</v>
+        <v>2796.68</v>
       </c>
     </row>
     <row r="458">
@@ -28389,7 +28389,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>2735.33</v>
+        <v>2748.07</v>
       </c>
     </row>
     <row r="459">
@@ -28450,7 +28450,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>946.89</v>
+        <v>951.3</v>
       </c>
     </row>
     <row r="460">
@@ -28511,7 +28511,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>24475.38</v>
+        <v>24589.36</v>
       </c>
     </row>
     <row r="461">
@@ -28572,7 +28572,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>1791.3</v>
+        <v>1799.64</v>
       </c>
     </row>
     <row r="462">
@@ -28633,7 +28633,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>2711.67</v>
+        <v>2724.3</v>
       </c>
     </row>
     <row r="463">
@@ -28694,7 +28694,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>10335.4</v>
+        <v>10383.53</v>
       </c>
     </row>
     <row r="464">
@@ -28755,7 +28755,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>1498.89</v>
+        <v>1505.87</v>
       </c>
     </row>
     <row r="465">
@@ -28816,7 +28816,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>754.86</v>
+        <v>758.38</v>
       </c>
     </row>
     <row r="466">
@@ -28877,7 +28877,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>2502.55</v>
+        <v>2514.2</v>
       </c>
     </row>
     <row r="467">
@@ -28938,7 +28938,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>2488.87</v>
+        <v>2500.46</v>
       </c>
     </row>
     <row r="468">
@@ -28999,7 +28999,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>2054.18</v>
+        <v>2063.74</v>
       </c>
     </row>
     <row r="469">
@@ -29060,7 +29060,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>8074.1</v>
+        <v>8111.71</v>
       </c>
     </row>
     <row r="470">
@@ -29121,7 +29121,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>2945.25</v>
+        <v>2958.97</v>
       </c>
     </row>
     <row r="471">
@@ -29182,7 +29182,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>3529.09</v>
+        <v>3545.53</v>
       </c>
     </row>
     <row r="472">
@@ -29243,7 +29243,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>11322.97</v>
+        <v>11375.71</v>
       </c>
     </row>
     <row r="473">
@@ -29304,7 +29304,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>4434.76</v>
+        <v>4455.42</v>
       </c>
     </row>
     <row r="474">
@@ -29365,7 +29365,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>2002.8</v>
+        <v>2012.12</v>
       </c>
     </row>
     <row r="475">
@@ -29426,7 +29426,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>20517.09</v>
+        <v>20612.65</v>
       </c>
     </row>
     <row r="476">
@@ -29487,7 +29487,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>838.23</v>
+        <v>842.13</v>
       </c>
     </row>
     <row r="477">
@@ -29548,7 +29548,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>1870.96</v>
+        <v>1879.68</v>
       </c>
     </row>
     <row r="478">
@@ -29609,7 +29609,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>4107.76</v>
+        <v>4126.89</v>
       </c>
     </row>
     <row r="479">
@@ -29670,7 +29670,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>2620.62</v>
+        <v>2632.83</v>
       </c>
     </row>
     <row r="480">
@@ -29731,7 +29731,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>4845.82</v>
+        <v>4868.39</v>
       </c>
     </row>
     <row r="481">
@@ -29792,7 +29792,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>10034.95</v>
+        <v>10107.3</v>
       </c>
     </row>
     <row r="482">
@@ -29853,7 +29853,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>3013.54</v>
+        <v>3035.27</v>
       </c>
     </row>
     <row r="483">
@@ -29914,7 +29914,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>2697.18</v>
+        <v>2716.62</v>
       </c>
     </row>
     <row r="484">
@@ -29975,7 +29975,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>4436.41</v>
+        <v>4468.39</v>
       </c>
     </row>
     <row r="485">
@@ -30036,7 +30036,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>34382.12</v>
+        <v>34630</v>
       </c>
     </row>
     <row r="486">
@@ -30097,7 +30097,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>7463.4</v>
+        <v>7517.21</v>
       </c>
     </row>
     <row r="487">
@@ -30158,7 +30158,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>2763.14</v>
+        <v>2783.06</v>
       </c>
     </row>
     <row r="488">
@@ -30219,7 +30219,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>11088.14</v>
+        <v>11168.07</v>
       </c>
     </row>
     <row r="489">
@@ -30280,7 +30280,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>22388.14</v>
+        <v>22549.55</v>
       </c>
     </row>
     <row r="490">
@@ -30341,7 +30341,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>1579.08</v>
+        <v>1590.46</v>
       </c>
     </row>
     <row r="491">
@@ -30402,7 +30402,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>3654.07</v>
+        <v>3680.42</v>
       </c>
     </row>
     <row r="492">
@@ -30463,7 +30463,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>2369.6</v>
+        <v>2386.69</v>
       </c>
     </row>
     <row r="493">
@@ -30524,7 +30524,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>14086.22</v>
+        <v>14187.77</v>
       </c>
     </row>
     <row r="494">
@@ -30585,7 +30585,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>25884.76</v>
+        <v>26071.38</v>
       </c>
     </row>
     <row r="495">
@@ -30646,7 +30646,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>4036.45</v>
+        <v>4065.55</v>
       </c>
     </row>
     <row r="496">
@@ -30707,7 +30707,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>9762.68</v>
+        <v>9833.059999999999</v>
       </c>
     </row>
     <row r="497">
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>6347.59</v>
+        <v>6393.35</v>
       </c>
     </row>
     <row r="498">
@@ -30829,7 +30829,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>1157.17</v>
+        <v>1165.51</v>
       </c>
     </row>
     <row r="499">
@@ -30890,7 +30890,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>2514.27</v>
+        <v>2532.4</v>
       </c>
     </row>
     <row r="500">
@@ -30951,7 +30951,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>2171.14</v>
+        <v>2186.79</v>
       </c>
     </row>
     <row r="501">
@@ -31012,7 +31012,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>7400.36</v>
+        <v>7453.72</v>
       </c>
     </row>
     <row r="502">
@@ -31073,7 +31073,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>1231.61</v>
+        <v>1240.49</v>
       </c>
     </row>
     <row r="503">
@@ -31134,7 +31134,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>2423.78</v>
+        <v>2441.25</v>
       </c>
     </row>
     <row r="504">
@@ -31195,7 +31195,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>3086.31</v>
+        <v>3108.56</v>
       </c>
     </row>
     <row r="505">
@@ -31256,7 +31256,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>7891.09</v>
+        <v>7947.98</v>
       </c>
     </row>
     <row r="506">
@@ -31317,7 +31317,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>10493.74</v>
+        <v>10569.4</v>
       </c>
     </row>
     <row r="507">
@@ -31378,7 +31378,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>1659.1</v>
+        <v>1671.06</v>
       </c>
     </row>
     <row r="508">
@@ -31439,7 +31439,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>745.37</v>
+        <v>750.75</v>
       </c>
     </row>
     <row r="509">
@@ -31500,7 +31500,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>1726.46</v>
+        <v>1738.9</v>
       </c>
     </row>
     <row r="510">
@@ -31561,7 +31561,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>2238.57</v>
+        <v>2254.71</v>
       </c>
     </row>
     <row r="511">
@@ -31622,7 +31622,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>8468.91</v>
+        <v>8529.959999999999</v>
       </c>
     </row>
     <row r="512">
@@ -31683,7 +31683,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>2246.53</v>
+        <v>2262.73</v>
       </c>
     </row>
     <row r="513">
@@ -31744,7 +31744,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>5163.52</v>
+        <v>5200.75</v>
       </c>
     </row>
     <row r="514">
@@ -31805,7 +31805,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>5332.92</v>
+        <v>5371.37</v>
       </c>
     </row>
     <row r="515">
@@ -31866,7 +31866,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>2022.89</v>
+        <v>2037.47</v>
       </c>
     </row>
     <row r="516">
@@ -31927,7 +31927,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>14056.69</v>
+        <v>14158.03</v>
       </c>
     </row>
     <row r="517">
@@ -31988,7 +31988,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>1042.4</v>
+        <v>1049.92</v>
       </c>
     </row>
     <row r="518">
@@ -32049,7 +32049,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>2209.77</v>
+        <v>2225.7</v>
       </c>
     </row>
     <row r="519">
@@ -32110,7 +32110,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>8004.67</v>
+        <v>8062.38</v>
       </c>
     </row>
     <row r="520">
@@ -32171,7 +32171,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>5011.87</v>
+        <v>5048</v>
       </c>
     </row>
     <row r="521">
@@ -32232,7 +32232,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>5215.56</v>
+        <v>5253.16</v>
       </c>
     </row>
     <row r="522">
@@ -32293,7 +32293,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>4738.49</v>
+        <v>4772.65</v>
       </c>
     </row>
     <row r="523">
@@ -32354,7 +32354,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>2682.59</v>
+        <v>2701.93</v>
       </c>
     </row>
     <row r="524">
@@ -32415,7 +32415,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>2242.99</v>
+        <v>2259.16</v>
       </c>
     </row>
     <row r="525">
@@ -32476,7 +32476,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>766.4400000000001</v>
+        <v>765.08</v>
       </c>
     </row>
     <row r="526">
@@ -32537,7 +32537,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>31146.17</v>
+        <v>31090.93</v>
       </c>
     </row>
     <row r="527">
@@ -32598,7 +32598,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>26370.2</v>
+        <v>26323.43</v>
       </c>
     </row>
     <row r="528">
@@ -32659,7 +32659,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>2277.08</v>
+        <v>2273.04</v>
       </c>
     </row>
     <row r="529">
@@ -32720,7 +32720,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>3377.32</v>
+        <v>3371.33</v>
       </c>
     </row>
     <row r="530">
@@ -32781,7 +32781,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>5222.87</v>
+        <v>5213.61</v>
       </c>
     </row>
     <row r="531">
@@ -32842,7 +32842,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>8184.89</v>
+        <v>8170.37</v>
       </c>
     </row>
     <row r="532">
@@ -32903,7 +32903,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>1602.34</v>
+        <v>1599.49</v>
       </c>
     </row>
     <row r="533">
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>2327.23</v>
+        <v>2323.1</v>
       </c>
     </row>
     <row r="534">
@@ -33025,7 +33025,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>3691.23</v>
+        <v>3684.69</v>
       </c>
     </row>
     <row r="535">
@@ -33086,7 +33086,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>2237.69</v>
+        <v>2233.73</v>
       </c>
     </row>
     <row r="536">
@@ -33147,7 +33147,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>1517.67</v>
+        <v>1514.98</v>
       </c>
     </row>
     <row r="537">
@@ -33208,7 +33208,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>7378.46</v>
+        <v>7365.38</v>
       </c>
     </row>
     <row r="538">
@@ -33269,7 +33269,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>2919.9</v>
+        <v>2914.72</v>
       </c>
     </row>
     <row r="539">
@@ -33330,7 +33330,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>4011.8</v>
+        <v>4004.68</v>
       </c>
     </row>
     <row r="540">
@@ -33391,7 +33391,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>7488.77</v>
+        <v>7475.49</v>
       </c>
     </row>
     <row r="541">
@@ -33452,7 +33452,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>8758.73</v>
+        <v>8743.200000000001</v>
       </c>
     </row>
     <row r="542">
@@ -33513,7 +33513,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>4110.39</v>
+        <v>4103.1</v>
       </c>
     </row>
     <row r="543">
@@ -33574,7 +33574,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>2680.53</v>
+        <v>2675.77</v>
       </c>
     </row>
     <row r="544">
@@ -33635,7 +33635,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>2584.5</v>
+        <v>2579.91</v>
       </c>
     </row>
     <row r="545">
@@ -33696,7 +33696,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>8010.41</v>
+        <v>7996.21</v>
       </c>
     </row>
     <row r="546">
@@ -33757,7 +33757,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>4713.33</v>
+        <v>4704.97</v>
       </c>
     </row>
     <row r="547">
@@ -33818,7 +33818,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>2138.05</v>
+        <v>2134.25</v>
       </c>
     </row>
     <row r="548">
@@ -33879,7 +33879,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>795.51</v>
+        <v>794.1</v>
       </c>
     </row>
     <row r="549">
@@ -33940,7 +33940,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>4918.6</v>
+        <v>4909.88</v>
       </c>
     </row>
     <row r="550">
@@ -34001,7 +34001,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>6301.03</v>
+        <v>6289.85</v>
       </c>
     </row>
     <row r="551">
@@ -34062,7 +34062,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>751.75</v>
+        <v>750.41</v>
       </c>
     </row>
     <row r="552">
@@ -34123,7 +34123,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>1646.06</v>
+        <v>1643.14</v>
       </c>
     </row>
     <row r="553">
@@ -34184,7 +34184,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>2920.96</v>
+        <v>2915.78</v>
       </c>
     </row>
     <row r="554">
@@ -34245,7 +34245,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>2582.68</v>
+        <v>2578.1</v>
       </c>
     </row>
     <row r="555">
@@ -34306,7 +34306,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>2135.04</v>
+        <v>2131.25</v>
       </c>
     </row>
     <row r="556">
@@ -34367,7 +34367,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>10771.46</v>
+        <v>10752.35</v>
       </c>
     </row>
     <row r="557">
@@ -34428,7 +34428,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>2243.96</v>
+        <v>2239.98</v>
       </c>
     </row>
     <row r="558">
@@ -34489,7 +34489,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>2268.24</v>
+        <v>2264.22</v>
       </c>
     </row>
     <row r="559">
@@ -34550,7 +34550,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>819.34</v>
+        <v>817.89</v>
       </c>
     </row>
     <row r="560">
@@ -34611,7 +34611,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>18786.95</v>
+        <v>18753.63</v>
       </c>
     </row>
     <row r="561">
@@ -34672,7 +34672,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>5721.81</v>
+        <v>5711.66</v>
       </c>
     </row>
     <row r="562">
@@ -34733,7 +34733,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>6145.74</v>
+        <v>6134.84</v>
       </c>
     </row>
     <row r="563">
@@ -34794,7 +34794,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>6125.96</v>
+        <v>6115.09</v>
       </c>
     </row>
     <row r="564">
@@ -34855,7 +34855,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>3427.11</v>
+        <v>3421.03</v>
       </c>
     </row>
     <row r="565">
@@ -34916,7 +34916,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>2480.29</v>
+        <v>2475.89</v>
       </c>
     </row>
     <row r="566">
@@ -34977,7 +34977,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>12793.91</v>
+        <v>12771.22</v>
       </c>
     </row>
     <row r="567">
@@ -35038,7 +35038,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>3751.95</v>
+        <v>3745.29</v>
       </c>
     </row>
     <row r="568">
@@ -35099,7 +35099,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>5155.58</v>
+        <v>5146.44</v>
       </c>
     </row>
     <row r="569">
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>10341.72</v>
+        <v>10323.38</v>
       </c>
     </row>
     <row r="570">
@@ -35221,7 +35221,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>4018.13</v>
+        <v>4011</v>
       </c>
     </row>
     <row r="571">
@@ -35282,7 +35282,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>749.4</v>
+        <v>748.0700000000001</v>
       </c>
     </row>
     <row r="572">
@@ -35343,7 +35343,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>2414.93</v>
+        <v>2410.65</v>
       </c>
     </row>
     <row r="573">
@@ -35404,7 +35404,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>3999.3</v>
+        <v>3992.21</v>
       </c>
     </row>
     <row r="574">
@@ -35465,7 +35465,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>3239.47</v>
+        <v>3233.73</v>
       </c>
     </row>
     <row r="575">
@@ -35526,7 +35526,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>2545.76</v>
+        <v>2535.27</v>
       </c>
     </row>
     <row r="576">
@@ -35587,7 +35587,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>2670.66</v>
+        <v>2659.66</v>
       </c>
     </row>
     <row r="577">
@@ -35648,7 +35648,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>8046.78</v>
+        <v>8013.62</v>
       </c>
     </row>
     <row r="578">
@@ -35709,7 +35709,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>3136.37</v>
+        <v>3123.44</v>
       </c>
     </row>
     <row r="579">
@@ -35770,7 +35770,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>19349.55</v>
+        <v>19269.8</v>
       </c>
     </row>
     <row r="580">
@@ -35831,7 +35831,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>9676.469999999999</v>
+        <v>9636.58</v>
       </c>
     </row>
     <row r="581">
@@ -35892,7 +35892,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>9795.9</v>
+        <v>9755.530000000001</v>
       </c>
     </row>
     <row r="582">
@@ -35953,7 +35953,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>3268.86</v>
+        <v>3255.39</v>
       </c>
     </row>
     <row r="583">
@@ -36014,7 +36014,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>5429.26</v>
+        <v>5406.88</v>
       </c>
     </row>
     <row r="584">
@@ -36075,7 +36075,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>2252.35</v>
+        <v>2243.06</v>
       </c>
     </row>
     <row r="585">
@@ -36136,7 +36136,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>11098.03</v>
+        <v>11052.29</v>
       </c>
     </row>
     <row r="586">
@@ -36197,7 +36197,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>6296.58</v>
+        <v>6270.62</v>
       </c>
     </row>
     <row r="587">
@@ -36258,7 +36258,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>1374.44</v>
+        <v>1368.78</v>
       </c>
     </row>
     <row r="588">
@@ -36319,7 +36319,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>1781.06</v>
+        <v>1773.72</v>
       </c>
     </row>
     <row r="589">
@@ -36380,7 +36380,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>5968.02</v>
+        <v>5943.42</v>
       </c>
     </row>
     <row r="590">
@@ -36441,7 +36441,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>12907.52</v>
+        <v>12854.32</v>
       </c>
     </row>
     <row r="591">
@@ -36502,7 +36502,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>1045.71</v>
+        <v>1041.4</v>
       </c>
     </row>
     <row r="592">
@@ -36563,7 +36563,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>5721.06</v>
+        <v>5697.48</v>
       </c>
     </row>
     <row r="593">
@@ -36624,7 +36624,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>2235.57</v>
+        <v>2226.36</v>
       </c>
     </row>
     <row r="594">
@@ -36685,7 +36685,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>2566.54</v>
+        <v>2555.96</v>
       </c>
     </row>
     <row r="595">
@@ -36746,7 +36746,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>6529.06</v>
+        <v>6502.15</v>
       </c>
     </row>
     <row r="596">
@@ -36807,7 +36807,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>5769.03</v>
+        <v>5745.25</v>
       </c>
     </row>
     <row r="597">
@@ -36868,7 +36868,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>4544.87</v>
+        <v>4526.14</v>
       </c>
     </row>
     <row r="598">
@@ -36929,7 +36929,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>8462.309999999999</v>
+        <v>8427.43</v>
       </c>
     </row>
     <row r="599">
@@ -36990,7 +36990,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>22981.79</v>
+        <v>22887.07</v>
       </c>
     </row>
     <row r="600">
@@ -37051,7 +37051,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>1972.63</v>
+        <v>1964.5</v>
       </c>
     </row>
     <row r="601">
@@ -37112,7 +37112,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>2525.09</v>
+        <v>2514.68</v>
       </c>
     </row>
     <row r="602">
@@ -37173,7 +37173,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>2071.47</v>
+        <v>2062.93</v>
       </c>
     </row>
     <row r="603">
@@ -37234,7 +37234,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>1360.85</v>
+        <v>1355.25</v>
       </c>
     </row>
     <row r="604">
@@ -37295,7 +37295,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>777.35</v>
+        <v>774.15</v>
       </c>
     </row>
     <row r="605">
@@ -37356,7 +37356,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>3162.04</v>
+        <v>3149.01</v>
       </c>
     </row>
     <row r="606">
@@ -37417,7 +37417,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>4064.73</v>
+        <v>4047.98</v>
       </c>
     </row>
     <row r="607">
@@ -37478,7 +37478,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>2234.84</v>
+        <v>2225.63</v>
       </c>
     </row>
     <row r="608">
@@ -37539,7 +37539,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>2231.92</v>
+        <v>2222.72</v>
       </c>
     </row>
     <row r="609">
@@ -37600,7 +37600,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>4243.51</v>
+        <v>4226.02</v>
       </c>
     </row>
     <row r="610">
@@ -37661,7 +37661,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>5532</v>
+        <v>5509.19</v>
       </c>
     </row>
     <row r="611">
@@ -37722,7 +37722,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>1598.88</v>
+        <v>1592.29</v>
       </c>
     </row>
     <row r="612">
@@ -37783,7 +37783,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>2763.23</v>
+        <v>2751.84</v>
       </c>
     </row>
     <row r="613">
@@ -37844,7 +37844,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>10601.62</v>
+        <v>10557.92</v>
       </c>
     </row>
     <row r="614">
@@ -37905,7 +37905,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>1236.17</v>
+        <v>1234.25</v>
       </c>
     </row>
     <row r="615">
@@ -37966,7 +37966,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>2943.79</v>
+        <v>2939.22</v>
       </c>
     </row>
     <row r="616">
@@ -38027,7 +38027,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>2352.13</v>
+        <v>2348.48</v>
       </c>
     </row>
     <row r="617">
@@ -38088,7 +38088,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>4926.59</v>
+        <v>4918.95</v>
       </c>
     </row>
     <row r="618">
@@ -38149,7 +38149,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>7081.26</v>
+        <v>7070.29</v>
       </c>
     </row>
     <row r="619">
@@ -38210,7 +38210,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>4611.21</v>
+        <v>4604.07</v>
       </c>
     </row>
     <row r="620">
@@ -38271,7 +38271,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>4285.57</v>
+        <v>4278.93</v>
       </c>
     </row>
     <row r="621">
@@ -38332,7 +38332,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>5572.77</v>
+        <v>5564.14</v>
       </c>
     </row>
     <row r="622">
@@ -38393,7 +38393,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>3436.09</v>
+        <v>3430.77</v>
       </c>
     </row>
     <row r="623">
@@ -38454,7 +38454,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>4048.96</v>
+        <v>4042.69</v>
       </c>
     </row>
     <row r="624">
@@ -38515,7 +38515,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>2225.15</v>
+        <v>2221.7</v>
       </c>
     </row>
     <row r="625">
@@ -38576,7 +38576,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>745.29</v>
+        <v>744.13</v>
       </c>
     </row>
     <row r="626">
@@ -38637,7 +38637,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>2957.26</v>
+        <v>2952.68</v>
       </c>
     </row>
     <row r="627">
@@ -38698,7 +38698,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>4315.65</v>
+        <v>4308.96</v>
       </c>
     </row>
     <row r="628">
@@ -38759,7 +38759,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>2511.51</v>
+        <v>2507.62</v>
       </c>
     </row>
     <row r="629">
@@ -38820,7 +38820,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>2576.73</v>
+        <v>2572.73</v>
       </c>
     </row>
     <row r="630">
@@ -38881,7 +38881,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>2808.54</v>
+        <v>2804.19</v>
       </c>
     </row>
     <row r="631">
@@ -38942,7 +38942,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>5544.57</v>
+        <v>5535.98</v>
       </c>
     </row>
     <row r="632">
@@ -39003,7 +39003,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>2144.27</v>
+        <v>2140.94</v>
       </c>
     </row>
     <row r="633">
@@ -39064,7 +39064,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>2579</v>
+        <v>2575.01</v>
       </c>
     </row>
     <row r="634">
@@ -39125,7 +39125,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>2689.42</v>
+        <v>2685.25</v>
       </c>
     </row>
     <row r="635">
@@ -39186,7 +39186,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>2477.31</v>
+        <v>2473.47</v>
       </c>
     </row>
     <row r="636">
@@ -39247,7 +39247,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>2240.9</v>
+        <v>2237.43</v>
       </c>
     </row>
     <row r="637">
@@ -39308,7 +39308,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>2130.61</v>
+        <v>2127.31</v>
       </c>
     </row>
     <row r="638">
@@ -39369,7 +39369,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>3585.09</v>
+        <v>3579.54</v>
       </c>
     </row>
     <row r="639">
@@ -39430,7 +39430,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>2243.53</v>
+        <v>2240.05</v>
       </c>
     </row>
     <row r="640">
@@ -39491,7 +39491,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>2991.4</v>
+        <v>3006.85</v>
       </c>
     </row>
     <row r="641">
@@ -39552,7 +39552,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>2754.27</v>
+        <v>2768.49</v>
       </c>
     </row>
     <row r="642">
@@ -39613,7 +39613,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>6986.63</v>
+        <v>7022.71</v>
       </c>
     </row>
     <row r="643">
@@ -39674,7 +39674,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>3054.65</v>
+        <v>3070.42</v>
       </c>
     </row>
     <row r="644">
@@ -39735,7 +39735,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>962.09</v>
+        <v>967.05</v>
       </c>
     </row>
     <row r="645">
@@ -39796,7 +39796,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>12504.71</v>
+        <v>12569.28</v>
       </c>
     </row>
     <row r="646">
@@ -39857,7 +39857,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>3201.03</v>
+        <v>3217.56</v>
       </c>
     </row>
     <row r="647">
@@ -39918,7 +39918,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>2718.43</v>
+        <v>2732.47</v>
       </c>
     </row>
     <row r="648">
@@ -39979,7 +39979,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>14842.01</v>
+        <v>14918.66</v>
       </c>
     </row>
     <row r="649">
@@ -40040,7 +40040,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>3501.07</v>
+        <v>3519.16</v>
       </c>
     </row>
     <row r="650">
@@ -40101,7 +40101,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>6631.61</v>
+        <v>6665.86</v>
       </c>
     </row>
     <row r="651">
@@ -40162,7 +40162,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>1827.7</v>
+        <v>1837.14</v>
       </c>
     </row>
     <row r="652">
@@ -40223,7 +40223,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>2221.74</v>
+        <v>2233.22</v>
       </c>
     </row>
     <row r="653">
@@ -40284,7 +40284,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>1601.21</v>
+        <v>1609.48</v>
       </c>
     </row>
     <row r="654">
@@ -40345,7 +40345,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>2235.72</v>
+        <v>2247.27</v>
       </c>
     </row>
     <row r="655">
@@ -40406,7 +40406,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>2285.09</v>
+        <v>2296.89</v>
       </c>
     </row>
     <row r="656">
@@ -40467,7 +40467,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>32062.19</v>
+        <v>32227.77</v>
       </c>
     </row>
     <row r="657">
@@ -40528,7 +40528,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>960.62</v>
+        <v>965.58</v>
       </c>
     </row>
     <row r="658">
@@ -40589,7 +40589,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>3278.19</v>
+        <v>3295.12</v>
       </c>
     </row>
     <row r="659">
@@ -40650,7 +40650,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>21197.03</v>
+        <v>21306.5</v>
       </c>
     </row>
     <row r="660">
@@ -40711,7 +40711,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>5801.73</v>
+        <v>5831.7</v>
       </c>
     </row>
     <row r="661">
@@ -40772,7 +40772,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>4257.91</v>
+        <v>4279.9</v>
       </c>
     </row>
     <row r="662">
@@ -40833,7 +40833,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>11037.94</v>
+        <v>11094.95</v>
       </c>
     </row>
     <row r="663">
@@ -40894,7 +40894,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>2943.36</v>
+        <v>2958.56</v>
       </c>
     </row>
     <row r="664">
@@ -40955,7 +40955,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>3563.52</v>
+        <v>3581.93</v>
       </c>
     </row>
     <row r="665">
@@ -41016,7 +41016,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>4444.1</v>
+        <v>4467.05</v>
       </c>
     </row>
     <row r="666">
@@ -41077,7 +41077,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>22665.27</v>
+        <v>22782.32</v>
       </c>
     </row>
     <row r="667">
@@ -41138,7 +41138,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>5335.8</v>
+        <v>5363.36</v>
       </c>
     </row>
     <row r="668">
@@ -41199,7 +41199,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>4622.72</v>
+        <v>4646.6</v>
       </c>
     </row>
     <row r="669">
@@ -41260,7 +41260,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>51158.25</v>
+        <v>51422.45</v>
       </c>
     </row>
     <row r="670">
@@ -41321,7 +41321,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>52922.52</v>
+        <v>53195.83</v>
       </c>
     </row>
     <row r="671">
@@ -41382,7 +41382,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>905.92</v>
+        <v>910.6</v>
       </c>
     </row>
     <row r="672">
@@ -41443,7 +41443,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>2338.39</v>
+        <v>2350.46</v>
       </c>
     </row>
     <row r="673">
@@ -41504,7 +41504,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>1208.18</v>
+        <v>1214.42</v>
       </c>
     </row>
     <row r="674">
@@ -41565,7 +41565,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>5525.18</v>
+        <v>5553.71</v>
       </c>
     </row>
     <row r="675">
@@ -41626,7 +41626,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>6026.48</v>
+        <v>6057.6</v>
       </c>
     </row>
     <row r="676">
@@ -41687,7 +41687,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>2426.18</v>
+        <v>2438.71</v>
       </c>
     </row>
     <row r="677">
@@ -41748,7 +41748,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>11308.59</v>
+        <v>11366.99</v>
       </c>
     </row>
     <row r="678">
@@ -41809,7 +41809,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>3962.23</v>
+        <v>3982.69</v>
       </c>
     </row>
     <row r="679">
@@ -41870,7 +41870,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>10104.28</v>
+        <v>10156.46</v>
       </c>
     </row>
     <row r="680">
@@ -41931,7 +41931,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>2304.49</v>
+        <v>2316.39</v>
       </c>
     </row>
     <row r="681">
@@ -41992,7 +41992,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>36858.65</v>
+        <v>37118.78</v>
       </c>
     </row>
     <row r="682">
@@ -42053,7 +42053,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>2457.32</v>
+        <v>2474.66</v>
       </c>
     </row>
     <row r="683">
@@ -42114,7 +42114,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>2352.08</v>
+        <v>2368.68</v>
       </c>
     </row>
     <row r="684">
@@ -42175,7 +42175,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>27645.03</v>
+        <v>27840.14</v>
       </c>
     </row>
     <row r="685">
@@ -42236,7 +42236,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>15652.8</v>
+        <v>15763.27</v>
       </c>
     </row>
     <row r="686">
@@ -42297,7 +42297,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>3213.94</v>
+        <v>3236.62</v>
       </c>
     </row>
     <row r="687">
@@ -42358,7 +42358,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>3810.53</v>
+        <v>3837.42</v>
       </c>
     </row>
     <row r="688">
@@ -42419,7 +42419,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>2231.59</v>
+        <v>2247.34</v>
       </c>
     </row>
     <row r="689">
@@ -42480,7 +42480,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>3964.6</v>
+        <v>3992.58</v>
       </c>
     </row>
     <row r="690">
@@ -42541,7 +42541,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>819.98</v>
+        <v>825.77</v>
       </c>
     </row>
     <row r="691">
@@ -42602,7 +42602,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>764.04</v>
+        <v>769.4299999999999</v>
       </c>
     </row>
     <row r="692">
@@ -42663,7 +42663,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>3723.81</v>
+        <v>3750.09</v>
       </c>
     </row>
     <row r="693">
@@ -42724,7 +42724,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>1738.39</v>
+        <v>1750.66</v>
       </c>
     </row>
     <row r="694">
@@ -42785,7 +42785,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>17307.68</v>
+        <v>17429.83</v>
       </c>
     </row>
     <row r="695">
@@ -42846,7 +42846,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>2323.41</v>
+        <v>2339.8</v>
       </c>
     </row>
     <row r="696">
@@ -42907,7 +42907,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>63090.73</v>
+        <v>63535.99</v>
       </c>
     </row>
     <row r="697">
@@ -42968,7 +42968,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>4067.15</v>
+        <v>4095.85</v>
       </c>
     </row>
     <row r="698">
@@ -43029,7 +43029,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>21208.39</v>
+        <v>21358.07</v>
       </c>
     </row>
     <row r="699">
@@ -43090,7 +43090,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>6953.2</v>
+        <v>7002.28</v>
       </c>
     </row>
     <row r="700">
@@ -43151,7 +43151,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>4687.47</v>
+        <v>4720.55</v>
       </c>
     </row>
     <row r="701">
@@ -43212,7 +43212,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>1828.5</v>
+        <v>1841.4</v>
       </c>
     </row>
     <row r="702">
@@ -43273,7 +43273,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>2963.94</v>
+        <v>2984.86</v>
       </c>
     </row>
     <row r="703">
@@ -43334,7 +43334,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>3206.06</v>
+        <v>3228.69</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/nov-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/nov-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC nov-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC nov-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14701,7 +14701,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -16657,7 +16657,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17572,7 +17572,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17694,7 +17694,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17877,7 +17877,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -19219,7 +19219,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -20317,7 +20317,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -21781,7 +21781,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -22879,7 +22879,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -22940,7 +22940,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -23855,7 +23855,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -24343,7 +24343,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -24404,7 +24404,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24587,7 +24587,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -24709,7 +24709,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -25197,7 +25197,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -25319,7 +25319,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25624,7 +25624,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -26112,7 +26112,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -27210,7 +27210,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -27820,7 +27820,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -28613,7 +28613,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -30016,7 +30016,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -30626,7 +30626,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -30687,7 +30687,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -30992,7 +30992,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -32883,7 +32883,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -32944,7 +32944,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -33127,7 +33127,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -33554,7 +33554,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -33615,7 +33615,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -33798,7 +33798,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -34225,7 +34225,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -34591,7 +34591,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -35018,7 +35018,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35506,7 +35506,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -36116,7 +36116,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -36482,7 +36482,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -37458,7 +37458,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -38800,7 +38800,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -39044,7 +39044,7 @@
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -39105,7 +39105,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -39166,7 +39166,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -39471,7 +39471,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -39715,7 +39715,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -39837,7 +39837,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -39959,7 +39959,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -40264,7 +40264,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -40508,7 +40508,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -40996,7 +40996,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -41484,7 +41484,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -43131,7 +43131,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -43192,7 +43192,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/nov-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/nov-2025.xlsx
@@ -562,7 +562,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1273,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1338,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1464,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1529,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1594,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1659,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1724,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1850,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1915,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2041,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2228,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2293,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2419,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2484,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2671,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2736,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2862,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3049,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3175,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3240,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3305,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3370,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3435,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3500,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3565,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3630,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3756,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3821,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3886,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3951,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4260,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4325,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4390,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4455,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4520,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4585,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4650,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4776,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4841,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4906,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4971,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5036,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5101,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5166,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5231,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5357,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5422,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5487,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5674,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5739,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5865,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5930,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6056,11 @@
           <t>77.577.274-3</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6121,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6247,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6312,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6438,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6503,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6629,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6694,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6759,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6824,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6889,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7015,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7141,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7206,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7271,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7397,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7523,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7588,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7653,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7718,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7783,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7848,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7913,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8100,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8165,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8230,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8295,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8360,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8425,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8551,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8616,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8681,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8746,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8811,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8876,11 @@
           <t>77.883.083-3</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8941,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9067,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9193,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9563,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9689,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9815,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10002,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10067,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10132,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10258,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10323,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10388,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10453,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10518,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10583,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10709,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10774,11 @@
           <t>77.714.552-5</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10839,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10904,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +10969,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11095,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11160,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11286,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11412,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11599,11 @@
           <t>77.577.274-3</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11725,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11790,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11855,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11920,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +11985,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12050,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12176,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12241,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12306,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12371,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12558,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12684,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12749,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12875,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12940,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13005,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13070,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13135,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13261,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13387,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13452,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13578,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13643,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13708,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13773,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13838,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13903,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +13968,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14155,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14220,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14346,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14411,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14537,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14663,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14789,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14854,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14919,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +14984,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15049,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15114,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15179,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15244,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15370,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15435,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15561,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15687,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +15752,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15939,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16004,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16069,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16134,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16199,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16264,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16329,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16455,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16520,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16646,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +16772,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16898,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17146,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17211,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17276,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16670,7 +17406,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16792,7 +17532,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16853,7 +17597,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16914,7 +17662,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16975,7 +17727,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17036,7 +17792,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17097,7 +17857,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17158,7 +17922,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17219,7 +17987,11 @@
           <t>77.649.678-2</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17341,7 +18113,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17402,7 +18178,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17463,7 +18243,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17585,7 +18369,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17646,7 +18434,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17768,7 +18560,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17829,7 +18625,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17890,7 +18690,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17951,7 +18755,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18012,7 +18820,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18073,7 +18885,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18317,7 +19133,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18378,7 +19198,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18439,7 +19263,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18500,7 +19328,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18683,7 +19515,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18744,7 +19580,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18805,7 +19645,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18866,7 +19710,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19049,7 +19897,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19110,7 +19962,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19171,7 +20027,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19232,7 +20092,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19476,7 +20340,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19659,7 +20527,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19720,7 +20592,11 @@
           <t>78.076.237-3</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19781,7 +20657,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19903,7 +20783,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19964,7 +20848,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20025,7 +20913,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20269,7 +21161,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20330,7 +21226,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20391,7 +21291,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20452,7 +21356,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20513,7 +21421,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20696,7 +21608,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20757,7 +21673,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20879,7 +21799,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20940,7 +21864,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21001,7 +21929,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21062,7 +21994,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21123,7 +22059,11 @@
           <t>78.076.237-3</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21245,7 +22185,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21306,7 +22250,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21367,7 +22315,11 @@
           <t>76.817.360-5</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21428,7 +22380,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21489,7 +22445,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21550,7 +22510,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21672,7 +22636,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21794,7 +22762,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21855,7 +22827,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21916,7 +22892,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22038,7 +23018,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22160,7 +23144,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22221,7 +23209,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22343,7 +23335,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22404,7 +23400,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22465,7 +23465,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22526,7 +23530,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22587,7 +23595,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22648,7 +23660,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22770,7 +23786,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22831,7 +23851,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22892,7 +23916,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22953,7 +23981,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23075,7 +24107,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23258,7 +24294,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23502,7 +24542,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23624,7 +24668,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23685,7 +24733,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23807,7 +24859,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23929,7 +24985,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23990,7 +25050,11 @@
           <t>77.630.237-6</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24112,7 +25176,11 @@
           <t>77.649.678-2</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24234,7 +25302,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24295,7 +25367,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24356,7 +25432,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24417,7 +25497,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24478,7 +25562,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24600,7 +25688,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24661,7 +25753,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24722,7 +25818,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24783,7 +25883,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24844,7 +25948,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24966,7 +26074,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25027,7 +26139,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25088,7 +26204,11 @@
           <t>78.076.237-3</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25149,7 +26269,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25210,7 +26334,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25393,7 +26521,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25515,7 +26647,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25576,7 +26712,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25637,7 +26777,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25698,7 +26842,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25820,7 +26968,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25881,7 +27033,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26003,7 +27159,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26064,7 +27224,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26125,7 +27289,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26186,7 +27354,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26247,7 +27419,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26308,7 +27484,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26369,7 +27549,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26491,7 +27675,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26552,7 +27740,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26613,7 +27805,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26674,7 +27870,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26735,7 +27935,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26796,7 +28000,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26918,7 +28126,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27101,7 +28313,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27162,7 +28378,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27284,7 +28504,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27345,7 +28569,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27406,7 +28634,11 @@
           <t>77.529.681-K</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27528,7 +28760,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27589,7 +28825,11 @@
           <t>77.577.274-3</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27711,7 +28951,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27772,7 +29016,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27833,7 +29081,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27894,7 +29146,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27955,7 +29211,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28016,7 +29276,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28260,7 +29524,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28382,7 +29650,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28443,7 +29715,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28565,7 +29841,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28748,7 +30028,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28809,7 +30093,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28870,7 +30158,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28931,7 +30223,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29053,7 +30349,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29114,7 +30414,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29297,7 +30601,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29358,7 +30666,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29480,7 +30792,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29541,7 +30857,11 @@
           <t>78.057.703-7</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29663,7 +30983,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29724,7 +31048,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29846,7 +31174,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30029,7 +31361,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30151,7 +31487,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30212,7 +31552,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30273,7 +31617,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30334,7 +31682,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30395,7 +31747,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30456,7 +31812,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30517,7 +31877,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30578,7 +31942,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30700,7 +32068,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30761,7 +32133,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30944,7 +32320,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31066,7 +32446,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31127,7 +32511,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31188,7 +32576,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31249,7 +32641,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31371,7 +32767,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31493,7 +32893,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31554,7 +32958,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31615,7 +33023,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31676,7 +33088,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31737,7 +33153,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31798,7 +33218,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31859,7 +33283,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31981,7 +33409,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32042,7 +33474,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32164,7 +33600,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32225,7 +33665,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32286,7 +33730,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32347,7 +33795,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32469,7 +33921,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32530,7 +33986,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32591,7 +34051,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32652,7 +34116,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32713,7 +34181,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32896,7 +34368,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32957,7 +34433,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33201,7 +34681,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33262,7 +34746,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33323,7 +34811,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33567,7 +35059,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33628,7 +35124,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33750,7 +35250,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33811,7 +35315,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33872,7 +35380,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33933,7 +35445,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34116,7 +35632,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34238,7 +35758,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34299,7 +35823,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34421,7 +35949,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34482,7 +36014,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34543,7 +36079,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34604,7 +36144,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34665,7 +36209,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34787,7 +36335,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34909,7 +36461,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35031,7 +36587,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35153,7 +36713,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35214,7 +36778,11 @@
           <t>77.577.274-3</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35275,7 +36843,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35336,7 +36908,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35397,7 +36973,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35458,7 +37038,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35580,7 +37164,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35641,7 +37229,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35702,7 +37294,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35824,7 +37420,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35885,7 +37485,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36007,7 +37611,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36068,7 +37676,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36129,7 +37741,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36251,7 +37867,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36312,7 +37932,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36373,7 +37997,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36434,7 +38062,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36495,7 +38127,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36556,7 +38192,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36617,7 +38257,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36678,7 +38322,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36739,7 +38387,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36800,7 +38452,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36861,7 +38517,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36922,7 +38582,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36983,7 +38647,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37105,7 +38773,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37227,7 +38899,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37410,7 +39086,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37471,7 +39151,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37532,7 +39216,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37593,7 +39281,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37654,7 +39346,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37715,7 +39411,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37776,7 +39476,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37837,7 +39541,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37898,7 +39606,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37959,7 +39671,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38020,7 +39736,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38081,7 +39801,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38142,7 +39866,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38264,7 +39992,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38325,7 +40057,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38386,7 +40122,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38447,7 +40187,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38508,7 +40252,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38569,7 +40317,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38630,7 +40382,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38691,7 +40447,11 @@
           <t>77.577.274-3</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38752,7 +40512,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38813,7 +40577,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38874,7 +40642,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38996,7 +40768,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39057,7 +40833,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39118,7 +40898,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39240,7 +41024,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39301,7 +41089,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39362,7 +41154,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39423,7 +41219,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39484,7 +41284,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39545,7 +41349,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39606,7 +41414,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39667,7 +41479,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39789,7 +41605,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39911,7 +41731,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39972,7 +41796,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40033,7 +41861,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40094,7 +41926,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40155,7 +41991,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40277,7 +42117,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40338,7 +42182,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40399,7 +42247,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40460,7 +42312,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40521,7 +42377,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40582,7 +42442,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40704,7 +42568,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40826,7 +42694,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40887,7 +42759,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41009,7 +42885,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41070,7 +42950,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41131,7 +43015,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41497,7 +43385,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41558,7 +43450,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41619,7 +43515,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41680,7 +43580,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41802,7 +43706,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41863,7 +43771,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41924,7 +43836,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41985,7 +43901,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42046,7 +43966,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42107,7 +44031,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42168,7 +44096,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42229,7 +44161,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42290,7 +44226,11 @@
           <t>76.525.922-3</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42351,7 +44291,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42412,7 +44356,11 @@
           <t>76.525.922-3</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42534,7 +44482,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42656,7 +44608,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42717,7 +44673,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42778,7 +44738,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42839,7 +44803,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42961,7 +44929,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43022,7 +44994,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43083,7 +45059,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L699" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43144,7 +45124,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43266,7 +45250,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L702" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43449,7 +45437,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K705" t="inlineStr"/>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L705" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/nov-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/nov-2025.xlsx
@@ -2358,7 +2358,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2549,7 +2553,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4715,7 +4723,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5995,7 +6007,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12436,7 +12452,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12814,7 +12834,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17471,7 +17495,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19454,7 +19482,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24172,7 +24204,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25115,7 +25151,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26586,7 +26626,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27098,7 +27142,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28065,7 +28113,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28890,7 +28942,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29402,7 +29458,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30288,7 +30348,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30540,7 +30604,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30922,7 +30990,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34246,7 +34318,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34559,7 +34635,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36274,7 +36354,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36652,7 +36736,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38712,7 +38800,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38838,7 +38930,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43202,7 +43298,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43263,7 +43363,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43645,7 +43749,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44421,7 +44529,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45189,7 +45301,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
